--- a/Assets/_Game/Introduce/基础召唤物/3费英雄.xlsx
+++ b/Assets/_Game/Introduce/基础召唤物/3费英雄.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2fdd5e1cd6b09a2c/Desktop/异界（Another World）/基础召唤物/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="492" documentId="11_AD4DA82427541F7ACA7EB89B78481DA46BE8DE12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C163582C-66D4-464F-A5C5-2AC32EB49A55}"/>
+  <xr:revisionPtr revIDLastSave="493" documentId="11_AD4DA82427541F7ACA7EB89B78481DA46BE8DE12" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2215F9F9-7E5D-4AAD-99C8-C5B8AE8B3BC7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,10 +427,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.当对方打出一张牌后，效果结算完成后，对对方一召唤物造成1伤害。（若为反制牌，打出后就造成伤害）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1.该召唤物导致的对方召唤物退场将不会触发退场</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -672,6 +668,10 @@
   </si>
   <si>
     <t>1.反击：选定一个格子，该格子上的召唤物临时+0-1（最少为0）并且每阶段开始扣一生命值   2.主动退场：选定两个格子，+1能量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.非攻击回合当对方打出一张牌后，效果结算完成后，对对方一召唤物造成1伤害。（若为反制牌，打出后就造成伤害）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -741,10 +741,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1043,7 +1039,7 @@
         <v>98</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -1060,7 +1056,7 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -1098,7 +1094,7 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
@@ -1113,7 +1109,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
@@ -1136,7 +1132,7 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>53</v>
@@ -1174,7 +1170,7 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
@@ -1212,7 +1208,7 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -1250,10 +1246,10 @@
     </row>
     <row r="7" spans="1:20" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>52</v>
@@ -1265,7 +1261,7 @@
         <v>99</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -1288,10 +1284,10 @@
     </row>
     <row r="8" spans="1:20" ht="28" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>52</v>
@@ -1303,7 +1299,7 @@
         <v>99</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G8" s="1">
         <v>2</v>
@@ -1326,7 +1322,7 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>10</v>
@@ -1341,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G9" s="1">
         <v>2</v>
@@ -1364,7 +1360,7 @@
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>11</v>
@@ -1402,7 +1398,7 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>12</v>
@@ -1440,7 +1436,7 @@
     </row>
     <row r="12" spans="1:20" ht="29" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>13</v>
@@ -1478,7 +1474,7 @@
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>14</v>
@@ -1493,7 +1489,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G13" s="1">
         <v>2</v>
@@ -1516,7 +1512,7 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>15</v>
@@ -1554,7 +1550,7 @@
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>16</v>
@@ -1592,7 +1588,7 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>17</v>
@@ -1630,7 +1626,7 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>18</v>
@@ -1668,7 +1664,7 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>19</v>
@@ -1706,7 +1702,7 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>20</v>
@@ -1744,7 +1740,7 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>21</v>
@@ -1782,7 +1778,7 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>22</v>
@@ -1820,7 +1816,7 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>23</v>
@@ -1858,7 +1854,7 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>24</v>
@@ -1896,7 +1892,7 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>25</v>
@@ -1934,7 +1930,7 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>26</v>
@@ -1972,7 +1968,7 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>27</v>
@@ -2010,7 +2006,7 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>28</v>
@@ -2048,7 +2044,7 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>29</v>
@@ -2086,7 +2082,7 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>30</v>
@@ -2124,7 +2120,7 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>31</v>
@@ -2162,7 +2158,7 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>32</v>
@@ -2177,7 +2173,7 @@
         <v>4</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G31" s="1">
         <v>2</v>
@@ -2200,7 +2196,7 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>33</v>
@@ -2215,7 +2211,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G32" s="1">
         <v>2</v>
@@ -2238,7 +2234,7 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>34</v>
@@ -2276,7 +2272,7 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>35</v>
@@ -2314,7 +2310,7 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>36</v>
@@ -2352,7 +2348,7 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>37</v>
@@ -2390,7 +2386,7 @@
     </row>
     <row r="37" spans="1:20" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>38</v>
@@ -2428,7 +2424,7 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>39</v>
@@ -2466,7 +2462,7 @@
     </row>
     <row r="39" spans="1:20" ht="28" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>40</v>
@@ -2481,7 +2477,7 @@
         <v>3</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G39" s="1">
         <v>2</v>
@@ -2504,7 +2500,7 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>41</v>
@@ -2519,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="G40" s="1">
         <v>2</v>
@@ -2542,7 +2538,7 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>42</v>
@@ -2580,7 +2576,7 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>43</v>
@@ -2618,7 +2614,7 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>44</v>
@@ -2656,7 +2652,7 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>45</v>
@@ -2694,7 +2690,7 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>46</v>
@@ -2732,7 +2728,7 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>47</v>
@@ -2770,7 +2766,7 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>48</v>
@@ -2808,7 +2804,7 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>49</v>
@@ -2846,7 +2842,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>50</v>
@@ -2872,7 +2868,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>51</v>
@@ -2887,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G50" s="1">
         <v>2</v>
